--- a/igrow_survey_responses.xlsx
+++ b/igrow_survey_responses.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,16 @@
           <t>Any suggestions or feedback for us?</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Your Name</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Community / Person who invited you</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,6 +493,41 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-08 04:48:10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>﻿One God, Three Persons</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>si jovs kasi nakatayo sya saka yung is this how you want to praise the Lord</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>doms</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>mama mo</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/igrow_survey_responses.xlsx
+++ b/igrow_survey_responses.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,39 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-08 04:50:44</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>﻿One God, Three Persons</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>mama mo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>hahaha</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>haha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/igrow_survey_responses.xlsx
+++ b/igrow_survey_responses.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,35 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-08 04:55:31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>﻿One God, Three Persons</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>mama ko</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>mama mo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/igrow_survey_responses.xlsx
+++ b/igrow_survey_responses.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,25 @@
           <t>mama nating lahat</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-13 11:10:49</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>﻿One God, Three Persons</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/igrow_survey_responses.xlsx
+++ b/igrow_survey_responses.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,43 +413,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Study Topic</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Your Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Community / Person who invited you</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Overall Satisfaction</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>What resonated with you most from today's study?</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Any suggestions or feedback for us?</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Group/Campus</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Satisfaction (1-5)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>What Resonated</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Suggestions</t>
         </is>
       </c>
     </row>
@@ -499,6 +512,11 @@
           <t>mama nating lahat</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,6 +536,35 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-01 03:47:30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sweet Scripture Secret</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
